--- a/home/roster.xlsx
+++ b/home/roster.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/home/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_D6E5441B28627EDC4691F04D3F68059E5C7A7665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5903E1-1834-440B-81CB-D043C7CFBF43}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="11_D6E5441B28627EDC4691F04D3F68059E5C7A7665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8DF7B22-233D-4C85-A700-15BFF3BD9355}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="737">
   <si>
     <t>player_id</t>
   </si>
@@ -2254,6 +2254,9 @@
   </si>
   <si>
     <t>Karim López</t>
+  </si>
+  <si>
+    <t>Christian Anderson Jr.</t>
   </si>
 </sst>
 </file>
@@ -2653,7 +2656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M444"/>
+  <dimension ref="A1:M445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -16923,6 +16926,38 @@
         <v>0</v>
       </c>
       <c r="K444" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="D445" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E445" s="1">
+        <v>0</v>
+      </c>
+      <c r="F445" s="1">
+        <v>0</v>
+      </c>
+      <c r="G445" s="1">
+        <v>0</v>
+      </c>
+      <c r="H445" s="1">
+        <v>0</v>
+      </c>
+      <c r="I445" s="1">
+        <v>0</v>
+      </c>
+      <c r="J445" s="1">
+        <v>0</v>
+      </c>
+      <c r="K445" s="1">
         <v>0</v>
       </c>
     </row>
@@ -25267,7 +25302,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -27410,59 +27445,68 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B103">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="C103">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D103">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="F103">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="H103">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
       <c r="I103" t="s">
         <v>620</v>
       </c>
       <c r="J103">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="K103" t="s">
         <v>620</v>
       </c>
       <c r="L103" t="str">
         <f>VLOOKUP(B103,players!A:B,2)</f>
-        <v>Darryn Peterson</v>
+        <v>Christian Anderson Jr.</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B104">
-        <v>242</v>
+        <v>420</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D104">
-        <v>3800000</v>
+        <v>6000000</v>
       </c>
       <c r="F104">
-        <v>4100000</v>
-      </c>
-      <c r="G104" t="s">
+        <v>6500000</v>
+      </c>
+      <c r="H104">
+        <v>7000000</v>
+      </c>
+      <c r="I104" t="s">
+        <v>620</v>
+      </c>
+      <c r="J104">
+        <v>7500000</v>
+      </c>
+      <c r="K104" t="s">
         <v>620</v>
       </c>
       <c r="L104" t="str">
         <f>VLOOKUP(B104,players!A:B,2)</f>
-        <v>Bub Carrington</v>
+        <v>Darryn Peterson</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -27470,14 +27514,23 @@
         <v>8</v>
       </c>
       <c r="B105">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>3800000</v>
+      </c>
+      <c r="F105">
+        <v>4100000</v>
+      </c>
+      <c r="G105" t="s">
+        <v>620</v>
       </c>
       <c r="L105" t="str">
         <f>VLOOKUP(B105,players!A:B,2)</f>
-        <v>Jrue Holiday</v>
+        <v>Bub Carrington</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -27485,29 +27538,14 @@
         <v>8</v>
       </c>
       <c r="B106">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="C106">
-        <v>3</v>
-      </c>
-      <c r="D106">
-        <v>1000000</v>
-      </c>
-      <c r="F106">
-        <v>1000000</v>
-      </c>
-      <c r="G106" t="s">
-        <v>620</v>
-      </c>
-      <c r="H106">
-        <v>1000000</v>
-      </c>
-      <c r="I106" t="s">
-        <v>620</v>
+        <v>2</v>
       </c>
       <c r="L106" t="str">
         <f>VLOOKUP(B106,players!A:B,2)</f>
-        <v>Cedric Coward</v>
+        <v>Jrue Holiday</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -27515,17 +27553,29 @@
         <v>8</v>
       </c>
       <c r="B107">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107">
-        <v>2000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="F107">
+        <v>1000000</v>
+      </c>
+      <c r="G107" t="s">
+        <v>620</v>
+      </c>
+      <c r="H107">
+        <v>1000000</v>
+      </c>
+      <c r="I107" t="s">
+        <v>620</v>
       </c>
       <c r="L107" t="str">
         <f>VLOOKUP(B107,players!A:B,2)</f>
-        <v>Aaron Gordon</v>
+        <v>Cedric Coward</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -27533,23 +27583,17 @@
         <v>8</v>
       </c>
       <c r="B108">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108">
-        <v>6000000</v>
-      </c>
-      <c r="F108">
-        <v>6000000</v>
-      </c>
-      <c r="H108">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="L108" t="str">
         <f>VLOOKUP(B108,players!A:B,2)</f>
-        <v>Kristaps Porziņģis</v>
+        <v>Aaron Gordon</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -27557,23 +27601,23 @@
         <v>8</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="C109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
       <c r="F109">
-        <v>7500000</v>
-      </c>
-      <c r="G109" t="s">
-        <v>620</v>
+        <v>6000000</v>
+      </c>
+      <c r="H109">
+        <v>6000000</v>
       </c>
       <c r="L109" t="str">
         <f>VLOOKUP(B109,players!A:B,2)</f>
-        <v>Donovan Clingan</v>
+        <v>Kristaps Porziņģis</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -27581,20 +27625,23 @@
         <v>8</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110">
-        <v>4000000</v>
+        <v>7000000</v>
       </c>
       <c r="F110">
-        <v>4000000</v>
+        <v>7500000</v>
+      </c>
+      <c r="G110" t="s">
+        <v>620</v>
       </c>
       <c r="L110" t="str">
         <f>VLOOKUP(B110,players!A:B,2)</f>
-        <v>Rudy Gobert</v>
+        <v>Donovan Clingan</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -27602,23 +27649,20 @@
         <v>8</v>
       </c>
       <c r="B111">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="F111">
-        <v>16000000</v>
-      </c>
-      <c r="H111">
-        <v>16000000</v>
+        <v>4000000</v>
       </c>
       <c r="L111" t="str">
         <f>VLOOKUP(B111,players!A:B,2)</f>
-        <v>Jalen Johnson</v>
+        <v>Rudy Gobert</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -27626,20 +27670,23 @@
         <v>8</v>
       </c>
       <c r="B112">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112">
-        <v>9000000</v>
+        <v>16000000</v>
       </c>
       <c r="F112">
-        <v>9000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="H112">
+        <v>16000000</v>
       </c>
       <c r="L112" t="str">
         <f>VLOOKUP(B112,players!A:B,2)</f>
-        <v>Trey Murphy III</v>
+        <v>Jalen Johnson</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -27647,17 +27694,20 @@
         <v>8</v>
       </c>
       <c r="B113">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C113">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D113">
-        <v>16000000</v>
+        <v>9000000</v>
+      </c>
+      <c r="F113">
+        <v>9000000</v>
       </c>
       <c r="L113" t="str">
         <f>VLOOKUP(B113,players!A:B,2)</f>
-        <v>Zion Williamson</v>
+        <v>Trey Murphy III</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -27665,23 +27715,17 @@
         <v>8</v>
       </c>
       <c r="B114">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="C114">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D114">
-        <v>19000000</v>
-      </c>
-      <c r="F114">
-        <v>19000000</v>
-      </c>
-      <c r="H114">
-        <v>19000000</v>
+        <v>16000000</v>
       </c>
       <c r="L114" t="str">
         <f>VLOOKUP(B114,players!A:B,2)</f>
-        <v>De'Aaron Fox</v>
+        <v>Zion Williamson</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -27689,14 +27733,23 @@
         <v>8</v>
       </c>
       <c r="B115">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="C115">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D115">
+        <v>19000000</v>
+      </c>
+      <c r="F115">
+        <v>19000000</v>
+      </c>
+      <c r="H115">
+        <v>19000000</v>
       </c>
       <c r="L115" t="str">
         <f>VLOOKUP(B115,players!A:B,2)</f>
-        <v>Norman Powell</v>
+        <v>De'Aaron Fox</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -27704,14 +27757,14 @@
         <v>8</v>
       </c>
       <c r="B116">
-        <v>59</v>
+        <v>225</v>
       </c>
       <c r="C116">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L116" t="str">
         <f>VLOOKUP(B116,players!A:B,2)</f>
-        <v>Dyson Daniels</v>
+        <v>Norman Powell</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -27719,14 +27772,14 @@
         <v>8</v>
       </c>
       <c r="B117">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="C117">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L117" t="str">
         <f>VLOOKUP(B117,players!A:B,2)</f>
-        <v>Collin Sexton</v>
+        <v>Dyson Daniels</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -27734,32 +27787,14 @@
         <v>8</v>
       </c>
       <c r="B118">
-        <v>428</v>
+        <v>336</v>
       </c>
       <c r="C118">
-        <v>15</v>
-      </c>
-      <c r="D118">
-        <v>3000000</v>
-      </c>
-      <c r="F118">
-        <v>3200000</v>
-      </c>
-      <c r="H118">
-        <v>3400000</v>
-      </c>
-      <c r="I118" t="s">
-        <v>620</v>
-      </c>
-      <c r="J118">
-        <v>3700000</v>
-      </c>
-      <c r="K118" t="s">
-        <v>620</v>
+        <v>14</v>
       </c>
       <c r="L118" t="str">
         <f>VLOOKUP(B118,players!A:B,2)</f>
-        <v>Aday Mara</v>
+        <v>Collin Sexton</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -27767,32 +27802,32 @@
         <v>8</v>
       </c>
       <c r="B119">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C119">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D119">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="F119">
-        <v>1000000</v>
+        <v>3200000</v>
       </c>
       <c r="H119">
-        <v>1000000</v>
+        <v>3400000</v>
       </c>
       <c r="I119" t="s">
         <v>620</v>
       </c>
       <c r="J119">
-        <v>1000000</v>
+        <v>3700000</v>
       </c>
       <c r="K119" t="s">
         <v>620</v>
       </c>
       <c r="L119" t="str">
         <f>VLOOKUP(B119,players!A:B,2)</f>
-        <v>Bennett Stirtz</v>
+        <v>Aday Mara</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -27800,10 +27835,10 @@
         <v>8</v>
       </c>
       <c r="B120">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C120">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D120">
         <v>1000000</v>
@@ -27825,31 +27860,40 @@
       </c>
       <c r="L120" t="str">
         <f>VLOOKUP(B120,players!A:B,2)</f>
-        <v>Chris Cenac Jr.</v>
+        <v>Bennett Stirtz</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D121">
-        <v>3100000</v>
+        <v>1000000</v>
       </c>
       <c r="F121">
-        <v>3100000</v>
+        <v>1000000</v>
       </c>
       <c r="H121">
-        <v>3100000</v>
+        <v>1000000</v>
+      </c>
+      <c r="I121" t="s">
+        <v>620</v>
+      </c>
+      <c r="J121">
+        <v>1000000</v>
+      </c>
+      <c r="K121" t="s">
+        <v>620</v>
       </c>
       <c r="L121" t="str">
         <f>VLOOKUP(B121,players!A:B,2)</f>
-        <v>Cam Thomas</v>
+        <v>Chris Cenac Jr.</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -27857,14 +27901,23 @@
         <v>9</v>
       </c>
       <c r="B122">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>3100000</v>
+      </c>
+      <c r="F122">
+        <v>3100000</v>
+      </c>
+      <c r="H122">
+        <v>3100000</v>
       </c>
       <c r="L122" t="str">
         <f>VLOOKUP(B122,players!A:B,2)</f>
-        <v>Ayo Dosunmu</v>
+        <v>Cam Thomas</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -27872,17 +27925,14 @@
         <v>9</v>
       </c>
       <c r="B123">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="C123">
-        <v>3</v>
-      </c>
-      <c r="D123">
-        <v>4500000</v>
+        <v>2</v>
       </c>
       <c r="L123" t="str">
         <f>VLOOKUP(B123,players!A:B,2)</f>
-        <v>Devin Vassell</v>
+        <v>Ayo Dosunmu</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -27890,14 +27940,17 @@
         <v>9</v>
       </c>
       <c r="B124">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="C124">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D124">
+        <v>4500000</v>
       </c>
       <c r="L124" t="str">
         <f>VLOOKUP(B124,players!A:B,2)</f>
-        <v>Rui Hachimura</v>
+        <v>Devin Vassell</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -27905,14 +27958,14 @@
         <v>9</v>
       </c>
       <c r="B125">
-        <v>416</v>
+        <v>251</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L125" t="str">
         <f>VLOOKUP(B125,players!A:B,2)</f>
-        <v>Clint Capela</v>
+        <v>Rui Hachimura</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -27920,23 +27973,14 @@
         <v>9</v>
       </c>
       <c r="B126">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="C126">
-        <v>6</v>
-      </c>
-      <c r="D126">
-        <v>3100000</v>
-      </c>
-      <c r="F126">
-        <v>3100000</v>
-      </c>
-      <c r="H126">
-        <v>3100000</v>
+        <v>5</v>
       </c>
       <c r="L126" t="str">
         <f>VLOOKUP(B126,players!A:B,2)</f>
-        <v>Jaden McDaniels</v>
+        <v>Clint Capela</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -27944,23 +27988,23 @@
         <v>9</v>
       </c>
       <c r="B127">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="F127">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="H127">
-        <v>32000000</v>
+        <v>3100000</v>
       </c>
       <c r="L127" t="str">
         <f>VLOOKUP(B127,players!A:B,2)</f>
-        <v>Jayson Tatum</v>
+        <v>Jaden McDaniels</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -27968,23 +28012,23 @@
         <v>9</v>
       </c>
       <c r="B128">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D128">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="F128">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="H128">
-        <v>12500000</v>
+        <v>32000000</v>
       </c>
       <c r="L128" t="str">
         <f>VLOOKUP(B128,players!A:B,2)</f>
-        <v>Jarrett Allen</v>
+        <v>Jayson Tatum</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -27992,17 +28036,23 @@
         <v>9</v>
       </c>
       <c r="B129">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D129">
-        <v>11500000</v>
+        <v>12500000</v>
+      </c>
+      <c r="F129">
+        <v>12500000</v>
+      </c>
+      <c r="H129">
+        <v>12500000</v>
       </c>
       <c r="L129" t="str">
         <f>VLOOKUP(B129,players!A:B,2)</f>
-        <v>Brandon Ingram</v>
+        <v>Jarrett Allen</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -28010,23 +28060,17 @@
         <v>9</v>
       </c>
       <c r="B130">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D130">
-        <v>3100000</v>
-      </c>
-      <c r="F130">
-        <v>3100000</v>
-      </c>
-      <c r="H130">
-        <v>3100000</v>
+        <v>11500000</v>
       </c>
       <c r="L130" t="str">
         <f>VLOOKUP(B130,players!A:B,2)</f>
-        <v>Shaedon Sharpe</v>
+        <v>Brandon Ingram</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -28034,17 +28078,23 @@
         <v>9</v>
       </c>
       <c r="B131">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="C131">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D131">
-        <v>25000000</v>
+        <v>3100000</v>
+      </c>
+      <c r="F131">
+        <v>3100000</v>
+      </c>
+      <c r="H131">
+        <v>3100000</v>
       </c>
       <c r="L131" t="str">
         <f>VLOOKUP(B131,players!A:B,2)</f>
-        <v>Stephen Curry</v>
+        <v>Shaedon Sharpe</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -28052,23 +28102,17 @@
         <v>9</v>
       </c>
       <c r="B132">
-        <v>331</v>
+        <v>217</v>
       </c>
       <c r="C132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D132">
-        <v>12000000</v>
-      </c>
-      <c r="F132">
-        <v>12000000</v>
-      </c>
-      <c r="H132">
-        <v>12000000</v>
+        <v>25000000</v>
       </c>
       <c r="L132" t="str">
         <f>VLOOKUP(B132,players!A:B,2)</f>
-        <v>Darius Garland</v>
+        <v>Stephen Curry</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -28076,62 +28120,71 @@
         <v>9</v>
       </c>
       <c r="B133">
-        <v>433</v>
+        <v>331</v>
       </c>
       <c r="C133">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D133">
-        <v>1000000</v>
+        <v>12000000</v>
       </c>
       <c r="F133">
-        <v>1000000</v>
+        <v>12000000</v>
       </c>
       <c r="H133">
-        <v>1000000</v>
-      </c>
-      <c r="I133" t="s">
-        <v>620</v>
-      </c>
-      <c r="J133">
-        <v>1000000</v>
-      </c>
-      <c r="K133" t="s">
-        <v>620</v>
+        <v>12000000</v>
       </c>
       <c r="L133" t="str">
         <f>VLOOKUP(B133,players!A:B,2)</f>
-        <v>Ebuka Okorie</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Darius Garland</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B134">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D134">
+        <v>1000000</v>
+      </c>
+      <c r="F134">
+        <v>1000000</v>
+      </c>
+      <c r="H134">
+        <v>1000000</v>
+      </c>
+      <c r="I134" t="s">
+        <v>620</v>
+      </c>
+      <c r="J134">
+        <v>1000000</v>
+      </c>
+      <c r="K134" t="s">
+        <v>620</v>
       </c>
       <c r="L134" t="str">
         <f>VLOOKUP(B134,players!A:B,2)</f>
-        <v>Walker Kessler</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+        <v>Ebuka Okorie</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>10</v>
       </c>
       <c r="B135">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="C135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L135" t="str">
         <f>VLOOKUP(B135,players!A:B,2)</f>
-        <v>Malik Monk</v>
+        <v>Walker Kessler</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -28139,14 +28192,14 @@
         <v>10</v>
       </c>
       <c r="B136">
-        <v>249</v>
+        <v>373</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L136" t="str">
         <f>VLOOKUP(B136,players!A:B,2)</f>
-        <v>Ajay Mitchell</v>
+        <v>Malik Monk</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -28154,17 +28207,14 @@
         <v>10</v>
       </c>
       <c r="B137">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="C137">
-        <v>4</v>
-      </c>
-      <c r="D137">
-        <v>4100000</v>
+        <v>3</v>
       </c>
       <c r="L137" t="str">
         <f>VLOOKUP(B137,players!A:B,2)</f>
-        <v>Bilal Coulibaly</v>
+        <v>Ajay Mitchell</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -28172,20 +28222,17 @@
         <v>10</v>
       </c>
       <c r="B138">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D138">
-        <v>6000000</v>
-      </c>
-      <c r="F138">
-        <v>6000000</v>
+        <v>4100000</v>
       </c>
       <c r="L138" t="str">
         <f>VLOOKUP(B138,players!A:B,2)</f>
-        <v>Mark Williams</v>
+        <v>Bilal Coulibaly</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -28193,17 +28240,20 @@
         <v>10</v>
       </c>
       <c r="B139">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="C139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D139">
-        <v>1000000</v>
+        <v>6000000</v>
+      </c>
+      <c r="F139">
+        <v>6000000</v>
       </c>
       <c r="L139" t="str">
         <f>VLOOKUP(B139,players!A:B,2)</f>
-        <v>GG Jackson II</v>
+        <v>Mark Williams</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -28211,14 +28261,17 @@
         <v>10</v>
       </c>
       <c r="B140">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D140">
+        <v>1000000</v>
       </c>
       <c r="L140" t="str">
         <f>VLOOKUP(B140,players!A:B,2)</f>
-        <v>Nikola Vučević</v>
+        <v>GG Jackson II</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -28226,23 +28279,14 @@
         <v>10</v>
       </c>
       <c r="B141">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C141">
-        <v>8</v>
-      </c>
-      <c r="D141">
-        <v>9250000</v>
-      </c>
-      <c r="F141">
-        <v>10000000</v>
-      </c>
-      <c r="G141" t="s">
-        <v>620</v>
+        <v>7</v>
       </c>
       <c r="L141" t="str">
         <f>VLOOKUP(B141,players!A:B,2)</f>
-        <v>Alex Sarr</v>
+        <v>Nikola Vučević</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -28250,23 +28294,23 @@
         <v>10</v>
       </c>
       <c r="B142">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C142">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D142">
-        <v>15000000</v>
+        <v>9250000</v>
       </c>
       <c r="F142">
-        <v>15000000</v>
-      </c>
-      <c r="H142">
-        <v>15000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="G142" t="s">
+        <v>620</v>
       </c>
       <c r="L142" t="str">
         <f>VLOOKUP(B142,players!A:B,2)</f>
-        <v>Julius Randle</v>
+        <v>Alex Sarr</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -28274,20 +28318,23 @@
         <v>10</v>
       </c>
       <c r="B143">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="C143">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D143">
-        <v>11000000</v>
+        <v>15000000</v>
       </c>
       <c r="F143">
-        <v>11000000</v>
+        <v>15000000</v>
+      </c>
+      <c r="H143">
+        <v>15000000</v>
       </c>
       <c r="L143" t="str">
         <f>VLOOKUP(B143,players!A:B,2)</f>
-        <v>Jalen Williams</v>
+        <v>Julius Randle</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -28295,23 +28342,20 @@
         <v>10</v>
       </c>
       <c r="B144">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C144">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D144">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="F144">
-        <v>16000000</v>
-      </c>
-      <c r="H144">
-        <v>16000000</v>
+        <v>11000000</v>
       </c>
       <c r="L144" t="str">
         <f>VLOOKUP(B144,players!A:B,2)</f>
-        <v>Jamal Murray</v>
+        <v>Jalen Williams</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -28319,17 +28363,23 @@
         <v>10</v>
       </c>
       <c r="B145">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="C145">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D145">
-        <v>24000000</v>
+        <v>16000000</v>
+      </c>
+      <c r="F145">
+        <v>16000000</v>
+      </c>
+      <c r="H145">
+        <v>16000000</v>
       </c>
       <c r="L145" t="str">
         <f>VLOOKUP(B145,players!A:B,2)</f>
-        <v>Jalen Brunson</v>
+        <v>Jamal Murray</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -28337,47 +28387,50 @@
         <v>10</v>
       </c>
       <c r="B146">
-        <v>443</v>
+        <v>246</v>
       </c>
       <c r="C146">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D146">
-        <v>1000000</v>
-      </c>
-      <c r="F146">
-        <v>1000000</v>
-      </c>
-      <c r="H146">
-        <v>1000000</v>
-      </c>
-      <c r="I146" t="s">
-        <v>620</v>
-      </c>
-      <c r="J146">
-        <v>1000000</v>
-      </c>
-      <c r="K146" t="s">
-        <v>620</v>
+        <v>24000000</v>
       </c>
       <c r="L146" t="str">
         <f>VLOOKUP(B146,players!A:B,2)</f>
-        <v>Zuby Ejiofor</v>
+        <v>Jalen Brunson</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B147">
-        <v>327</v>
+        <v>443</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D147">
+        <v>1000000</v>
+      </c>
+      <c r="F147">
+        <v>1000000</v>
+      </c>
+      <c r="H147">
+        <v>1000000</v>
+      </c>
+      <c r="I147" t="s">
+        <v>620</v>
+      </c>
+      <c r="J147">
+        <v>1000000</v>
+      </c>
+      <c r="K147" t="s">
+        <v>620</v>
       </c>
       <c r="L147" t="str">
         <f>VLOOKUP(B147,players!A:B,2)</f>
-        <v>Cole Anthony</v>
+        <v>Zuby Ejiofor</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -28385,14 +28438,14 @@
         <v>11</v>
       </c>
       <c r="B148">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L148" t="str">
         <f>VLOOKUP(B148,players!A:B,2)</f>
-        <v>Khris Middleton</v>
+        <v>Cole Anthony</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -28400,17 +28453,14 @@
         <v>11</v>
       </c>
       <c r="B149">
-        <v>111</v>
+        <v>213</v>
       </c>
       <c r="C149">
-        <v>3</v>
-      </c>
-      <c r="D149">
-        <v>1000000</v>
+        <v>2</v>
       </c>
       <c r="L149" t="str">
         <f>VLOOKUP(B149,players!A:B,2)</f>
-        <v>John Collins</v>
+        <v>Khris Middleton</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -28418,14 +28468,17 @@
         <v>11</v>
       </c>
       <c r="B150">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C150">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D150">
+        <v>1000000</v>
       </c>
       <c r="L150" t="str">
         <f>VLOOKUP(B150,players!A:B,2)</f>
-        <v>Daniel Gafford</v>
+        <v>John Collins</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -28433,17 +28486,14 @@
         <v>11</v>
       </c>
       <c r="B151">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C151">
-        <v>5</v>
-      </c>
-      <c r="D151">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L151" t="str">
         <f>VLOOKUP(B151,players!A:B,2)</f>
-        <v>Isaiah Hartenstein</v>
+        <v>Daniel Gafford</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -28451,14 +28501,17 @@
         <v>11</v>
       </c>
       <c r="B152">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C152">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D152">
+        <v>1000000</v>
       </c>
       <c r="L152" t="str">
         <f>VLOOKUP(B152,players!A:B,2)</f>
-        <v>Jalen Smith</v>
+        <v>Isaiah Hartenstein</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -28466,17 +28519,14 @@
         <v>11</v>
       </c>
       <c r="B153">
+        <v>63</v>
+      </c>
+      <c r="C153">
         <v>6</v>
-      </c>
-      <c r="C153">
-        <v>7</v>
-      </c>
-      <c r="D153">
-        <v>26000000</v>
       </c>
       <c r="L153" t="str">
         <f>VLOOKUP(B153,players!A:B,2)</f>
-        <v>Domantas Sabonis</v>
+        <v>Jalen Smith</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -28484,17 +28534,17 @@
         <v>11</v>
       </c>
       <c r="B154">
-        <v>177</v>
+        <v>6</v>
       </c>
       <c r="C154">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D154">
-        <v>15000000</v>
+        <v>26000000</v>
       </c>
       <c r="L154" t="str">
         <f>VLOOKUP(B154,players!A:B,2)</f>
-        <v>Desmond Bane</v>
+        <v>Domantas Sabonis</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -28502,17 +28552,17 @@
         <v>11</v>
       </c>
       <c r="B155">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="C155">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D155">
-        <v>7500000</v>
+        <v>15000000</v>
       </c>
       <c r="L155" t="str">
         <f>VLOOKUP(B155,players!A:B,2)</f>
-        <v>Amen Thompson</v>
+        <v>Desmond Bane</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -28520,23 +28570,17 @@
         <v>11</v>
       </c>
       <c r="B156">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="C156">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D156">
-        <v>30000000</v>
-      </c>
-      <c r="F156">
-        <v>30000000</v>
-      </c>
-      <c r="H156">
-        <v>30000000</v>
+        <v>7500000</v>
       </c>
       <c r="L156" t="str">
         <f>VLOOKUP(B156,players!A:B,2)</f>
-        <v>Shai Gilgeous-Alexander</v>
+        <v>Amen Thompson</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -28544,17 +28588,23 @@
         <v>11</v>
       </c>
       <c r="B157">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="C157">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D157">
-        <v>1000000</v>
+        <v>30000000</v>
+      </c>
+      <c r="F157">
+        <v>30000000</v>
+      </c>
+      <c r="H157">
+        <v>30000000</v>
       </c>
       <c r="L157" t="str">
         <f>VLOOKUP(B157,players!A:B,2)</f>
-        <v>CJ McCollum</v>
+        <v>Shai Gilgeous-Alexander</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -28562,14 +28612,17 @@
         <v>11</v>
       </c>
       <c r="B158">
-        <v>109</v>
+        <v>248</v>
       </c>
       <c r="C158">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D158">
+        <v>1000000</v>
       </c>
       <c r="L158" t="str">
         <f>VLOOKUP(B158,players!A:B,2)</f>
-        <v>Paul George</v>
+        <v>CJ McCollum</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -28577,14 +28630,14 @@
         <v>11</v>
       </c>
       <c r="B159">
-        <v>266</v>
+        <v>109</v>
       </c>
       <c r="C159">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L159" t="str">
         <f>VLOOKUP(B159,players!A:B,2)</f>
-        <v>Moritz Wagner</v>
+        <v>Paul George</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -28592,14 +28645,14 @@
         <v>11</v>
       </c>
       <c r="B160">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="C160">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L160" t="str">
         <f>VLOOKUP(B160,players!A:B,2)</f>
-        <v>Payton Pritchard</v>
+        <v>Moritz Wagner</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -28607,53 +28660,47 @@
         <v>11</v>
       </c>
       <c r="B161">
-        <v>436</v>
+        <v>195</v>
       </c>
       <c r="C161">
-        <v>15</v>
-      </c>
-      <c r="D161">
-        <v>1000000</v>
-      </c>
-      <c r="F161">
-        <v>1000000</v>
-      </c>
-      <c r="H161">
-        <v>1000000</v>
-      </c>
-      <c r="I161" t="s">
-        <v>620</v>
-      </c>
-      <c r="J161">
-        <v>1000000</v>
-      </c>
-      <c r="K161" t="s">
-        <v>620</v>
+        <v>14</v>
       </c>
       <c r="L161" t="str">
         <f>VLOOKUP(B161,players!A:B,2)</f>
-        <v>Meleek Thomas</v>
+        <v>Payton Pritchard</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B162">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D162">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="F162">
-        <v>5000000</v>
+        <v>1000000</v>
+      </c>
+      <c r="H162">
+        <v>1000000</v>
+      </c>
+      <c r="I162" t="s">
+        <v>620</v>
+      </c>
+      <c r="J162">
+        <v>1000000</v>
+      </c>
+      <c r="K162" t="s">
+        <v>620</v>
       </c>
       <c r="L162" t="str">
         <f>VLOOKUP(B162,players!A:B,2)</f>
-        <v>Bradley Beal</v>
+        <v>Meleek Thomas</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -28661,20 +28708,20 @@
         <v>12</v>
       </c>
       <c r="B163">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="F163">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="L163" t="str">
         <f>VLOOKUP(B163,players!A:B,2)</f>
-        <v>Buddy Hield</v>
+        <v>Bradley Beal</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -28682,17 +28729,20 @@
         <v>12</v>
       </c>
       <c r="B164">
-        <v>120</v>
+        <v>345</v>
       </c>
       <c r="C164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D164">
-        <v>1000000</v>
+        <v>3500000</v>
+      </c>
+      <c r="F164">
+        <v>3500000</v>
       </c>
       <c r="L164" t="str">
         <f>VLOOKUP(B164,players!A:B,2)</f>
-        <v>Brandin Podziemski</v>
+        <v>Buddy Hield</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -28700,14 +28750,17 @@
         <v>12</v>
       </c>
       <c r="B165">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="C165">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D165">
+        <v>1000000</v>
       </c>
       <c r="L165" t="str">
         <f>VLOOKUP(B165,players!A:B,2)</f>
-        <v>Chet Holmgren</v>
+        <v>Brandin Podziemski</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -28715,17 +28768,14 @@
         <v>12</v>
       </c>
       <c r="B166">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C166">
-        <v>5</v>
-      </c>
-      <c r="D166">
-        <v>11000000</v>
+        <v>4</v>
       </c>
       <c r="L166" t="str">
         <f>VLOOKUP(B166,players!A:B,2)</f>
-        <v>Lauri Markkanen</v>
+        <v>Chet Holmgren</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -28733,20 +28783,17 @@
         <v>12</v>
       </c>
       <c r="B167">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="C167">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D167">
-        <v>20000000</v>
-      </c>
-      <c r="F167">
-        <v>20000000</v>
+        <v>11000000</v>
       </c>
       <c r="L167" t="str">
         <f>VLOOKUP(B167,players!A:B,2)</f>
-        <v>Devin Booker</v>
+        <v>Lauri Markkanen</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -28754,23 +28801,20 @@
         <v>12</v>
       </c>
       <c r="B168">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="C168">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D168">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="F168">
-        <v>18000000</v>
-      </c>
-      <c r="H168">
-        <v>18000000</v>
+        <v>20000000</v>
       </c>
       <c r="L168" t="str">
         <f>VLOOKUP(B168,players!A:B,2)</f>
-        <v>Tyrese Haliburton</v>
+        <v>Devin Booker</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -28778,17 +28822,23 @@
         <v>12</v>
       </c>
       <c r="B169">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="C169">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D169">
-        <v>2500000</v>
+        <v>18000000</v>
+      </c>
+      <c r="F169">
+        <v>18000000</v>
+      </c>
+      <c r="H169">
+        <v>18000000</v>
       </c>
       <c r="L169" t="str">
         <f>VLOOKUP(B169,players!A:B,2)</f>
-        <v>Kevin Porter Jr.</v>
+        <v>Tyrese Haliburton</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -28796,32 +28846,17 @@
         <v>12</v>
       </c>
       <c r="B170">
-        <v>417</v>
+        <v>115</v>
       </c>
       <c r="C170">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D170">
-        <v>9000000</v>
-      </c>
-      <c r="F170">
-        <v>9500000</v>
-      </c>
-      <c r="H170">
-        <v>10500000</v>
-      </c>
-      <c r="I170" t="s">
-        <v>620</v>
-      </c>
-      <c r="J170">
-        <v>11500000</v>
-      </c>
-      <c r="K170" t="s">
-        <v>620</v>
+        <v>2500000</v>
       </c>
       <c r="L170" t="str">
         <f>VLOOKUP(B170,players!A:B,2)</f>
-        <v>A.J. Dybantsa</v>
+        <v>Kevin Porter Jr.</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -28829,50 +28864,65 @@
         <v>12</v>
       </c>
       <c r="B171">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="C171">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D171">
-        <v>1000000</v>
+        <v>9000000</v>
       </c>
       <c r="F171">
-        <v>1000000</v>
+        <v>9500000</v>
       </c>
       <c r="H171">
-        <v>1000000</v>
+        <v>10500000</v>
       </c>
       <c r="I171" t="s">
         <v>620</v>
       </c>
       <c r="J171">
-        <v>1000000</v>
+        <v>11500000</v>
       </c>
       <c r="K171" t="s">
         <v>620</v>
       </c>
       <c r="L171" t="str">
         <f>VLOOKUP(B171,players!A:B,2)</f>
-        <v>Nate Ament</v>
+        <v>A.J. Dybantsa</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B172">
-        <v>307</v>
+        <v>431</v>
       </c>
       <c r="C172">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D172">
         <v>1000000</v>
       </c>
+      <c r="F172">
+        <v>1000000</v>
+      </c>
+      <c r="H172">
+        <v>1000000</v>
+      </c>
+      <c r="I172" t="s">
+        <v>620</v>
+      </c>
+      <c r="J172">
+        <v>1000000</v>
+      </c>
+      <c r="K172" t="s">
+        <v>620</v>
+      </c>
       <c r="L172" t="str">
         <f>VLOOKUP(B172,players!A:B,2)</f>
-        <v>Davion Mitchell</v>
+        <v>Nate Ament</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -28880,14 +28930,17 @@
         <v>13</v>
       </c>
       <c r="B173">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="C173">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>1000000</v>
       </c>
       <c r="L173" t="str">
         <f>VLOOKUP(B173,players!A:B,2)</f>
-        <v>Jordan Poole</v>
+        <v>Davion Mitchell</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -28895,17 +28948,14 @@
         <v>13</v>
       </c>
       <c r="B174">
-        <v>296</v>
+        <v>363</v>
       </c>
       <c r="C174">
-        <v>3</v>
-      </c>
-      <c r="D174">
-        <v>3000000</v>
+        <v>2</v>
       </c>
       <c r="L174" t="str">
         <f>VLOOKUP(B174,players!A:B,2)</f>
-        <v>Andrew Nembhard</v>
+        <v>Jordan Poole</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -28913,17 +28963,17 @@
         <v>13</v>
       </c>
       <c r="B175">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="C175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D175">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="L175" t="str">
         <f>VLOOKUP(B175,players!A:B,2)</f>
-        <v>Aaron Nesmith</v>
+        <v>Andrew Nembhard</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -28931,14 +28981,17 @@
         <v>13</v>
       </c>
       <c r="B176">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="C176">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D176">
+        <v>2000000</v>
       </c>
       <c r="L176" t="str">
         <f>VLOOKUP(B176,players!A:B,2)</f>
-        <v>Ivica Zubac</v>
+        <v>Aaron Nesmith</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -28946,14 +28999,14 @@
         <v>13</v>
       </c>
       <c r="B177">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C177">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L177" t="str">
         <f>VLOOKUP(B177,players!A:B,2)</f>
-        <v>Wendell Carter Jr.</v>
+        <v>Ivica Zubac</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -28961,17 +29014,14 @@
         <v>13</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C178">
-        <v>7</v>
-      </c>
-      <c r="D178">
-        <v>11500000</v>
+        <v>6</v>
       </c>
       <c r="L178" t="str">
         <f>VLOOKUP(B178,players!A:B,2)</f>
-        <v>Victor Wembanyama</v>
+        <v>Wendell Carter Jr.</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -28979,23 +29029,17 @@
         <v>13</v>
       </c>
       <c r="B179">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C179">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D179">
-        <v>16000000</v>
-      </c>
-      <c r="F179">
-        <v>16000000</v>
-      </c>
-      <c r="H179">
-        <v>16000000</v>
+        <v>11500000</v>
       </c>
       <c r="L179" t="str">
         <f>VLOOKUP(B179,players!A:B,2)</f>
-        <v>Josh Giddey</v>
+        <v>Victor Wembanyama</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -29003,23 +29047,23 @@
         <v>13</v>
       </c>
       <c r="B180">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C180">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D180">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="F180">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="H180">
-        <v>12000000</v>
+        <v>16000000</v>
       </c>
       <c r="L180" t="str">
         <f>VLOOKUP(B180,players!A:B,2)</f>
-        <v>Deni Avdija</v>
+        <v>Josh Giddey</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -29027,17 +29071,23 @@
         <v>13</v>
       </c>
       <c r="B181">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C181">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D181">
-        <v>19000000</v>
+        <v>12000000</v>
+      </c>
+      <c r="F181">
+        <v>12000000</v>
+      </c>
+      <c r="H181">
+        <v>12000000</v>
       </c>
       <c r="L181" t="str">
         <f>VLOOKUP(B181,players!A:B,2)</f>
-        <v>Pascal Siakam</v>
+        <v>Deni Avdija</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -29045,23 +29095,17 @@
         <v>13</v>
       </c>
       <c r="B182">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="C182">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D182">
-        <v>6000000</v>
-      </c>
-      <c r="F182">
-        <v>6000000</v>
-      </c>
-      <c r="H182">
-        <v>6000000</v>
+        <v>19000000</v>
       </c>
       <c r="L182" t="str">
         <f>VLOOKUP(B182,players!A:B,2)</f>
-        <v>Austin Reaves</v>
+        <v>Pascal Siakam</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -29069,32 +29113,23 @@
         <v>13</v>
       </c>
       <c r="B183">
-        <v>430</v>
+        <v>150</v>
       </c>
       <c r="C183">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D183">
-        <v>2600000</v>
+        <v>6000000</v>
       </c>
       <c r="F183">
-        <v>2800000</v>
+        <v>6000000</v>
       </c>
       <c r="H183">
-        <v>3000000</v>
-      </c>
-      <c r="I183" t="s">
-        <v>620</v>
-      </c>
-      <c r="J183">
-        <v>3300000</v>
-      </c>
-      <c r="K183" t="s">
-        <v>620</v>
+        <v>6000000</v>
       </c>
       <c r="L183" t="str">
         <f>VLOOKUP(B183,players!A:B,2)</f>
-        <v>Cameron Carr</v>
+        <v>Austin Reaves</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -29102,47 +29137,65 @@
         <v>13</v>
       </c>
       <c r="B184">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C184">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D184">
-        <v>1000000</v>
+        <v>2600000</v>
       </c>
       <c r="F184">
-        <v>1000000</v>
+        <v>2800000</v>
       </c>
       <c r="H184">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="I184" t="s">
         <v>620</v>
       </c>
       <c r="J184">
-        <v>1000000</v>
+        <v>3300000</v>
       </c>
       <c r="K184" t="s">
         <v>620</v>
       </c>
       <c r="L184" t="str">
         <f>VLOOKUP(B184,players!A:B,2)</f>
-        <v>Sergio de Larrea</v>
+        <v>Cameron Carr</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185">
+        <v>13</v>
+      </c>
+      <c r="B185">
+        <v>440</v>
+      </c>
+      <c r="C185">
         <v>14</v>
       </c>
-      <c r="B185">
-        <v>317</v>
-      </c>
-      <c r="C185">
-        <v>1</v>
+      <c r="D185">
+        <v>1000000</v>
+      </c>
+      <c r="F185">
+        <v>1000000</v>
+      </c>
+      <c r="H185">
+        <v>1000000</v>
+      </c>
+      <c r="I185" t="s">
+        <v>620</v>
+      </c>
+      <c r="J185">
+        <v>1000000</v>
+      </c>
+      <c r="K185" t="s">
+        <v>620</v>
       </c>
       <c r="L185" t="str">
         <f>VLOOKUP(B185,players!A:B,2)</f>
-        <v>Anfernee Simons</v>
+        <v>Sergio de Larrea</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -29150,14 +29203,14 @@
         <v>14</v>
       </c>
       <c r="B186">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L186" t="str">
         <f>VLOOKUP(B186,players!A:B,2)</f>
-        <v>Marcus Smart</v>
+        <v>Anfernee Simons</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -29165,14 +29218,14 @@
         <v>14</v>
       </c>
       <c r="B187">
-        <v>129</v>
+        <v>299</v>
       </c>
       <c r="C187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L187" t="str">
         <f>VLOOKUP(B187,players!A:B,2)</f>
-        <v>Jaime Jaquez Jr.</v>
+        <v>Marcus Smart</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -29180,14 +29233,14 @@
         <v>14</v>
       </c>
       <c r="B188">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L188" t="str">
         <f>VLOOKUP(B188,players!A:B,2)</f>
-        <v>Jimmy Butler</v>
+        <v>Jaime Jaquez Jr.</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -29195,17 +29248,14 @@
         <v>14</v>
       </c>
       <c r="B189">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="C189">
-        <v>5</v>
-      </c>
-      <c r="D189">
-        <v>1000000</v>
+        <v>4</v>
       </c>
       <c r="L189" t="str">
         <f>VLOOKUP(B189,players!A:B,2)</f>
-        <v>Moussa Diabaté</v>
+        <v>Jimmy Butler</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -29213,17 +29263,17 @@
         <v>14</v>
       </c>
       <c r="B190">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="C190">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D190">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="L190" t="str">
         <f>VLOOKUP(B190,players!A:B,2)</f>
-        <v>Coby White</v>
+        <v>Moussa Diabaté</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -29231,23 +29281,17 @@
         <v>14</v>
       </c>
       <c r="B191">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="C191">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D191">
-        <v>20500000</v>
-      </c>
-      <c r="F191">
-        <v>20500000</v>
-      </c>
-      <c r="H191">
-        <v>20500000</v>
+        <v>3000000</v>
       </c>
       <c r="L191" t="str">
         <f>VLOOKUP(B191,players!A:B,2)</f>
-        <v>Evan Mobley</v>
+        <v>Coby White</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -29255,17 +29299,23 @@
         <v>14</v>
       </c>
       <c r="B192">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C192">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D192">
-        <v>19500000</v>
+        <v>20500000</v>
+      </c>
+      <c r="F192">
+        <v>20500000</v>
+      </c>
+      <c r="H192">
+        <v>20500000</v>
       </c>
       <c r="L192" t="str">
         <f>VLOOKUP(B192,players!A:B,2)</f>
-        <v>LeBron James</v>
+        <v>Evan Mobley</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -29273,29 +29323,17 @@
         <v>14</v>
       </c>
       <c r="B193">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C193">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D193">
-        <v>9500000</v>
-      </c>
-      <c r="F193">
-        <v>10500000</v>
-      </c>
-      <c r="G193" t="s">
-        <v>620</v>
-      </c>
-      <c r="H193">
-        <v>11500000</v>
-      </c>
-      <c r="I193" t="s">
-        <v>620</v>
+        <v>19500000</v>
       </c>
       <c r="L193" t="str">
         <f>VLOOKUP(B193,players!A:B,2)</f>
-        <v>Cooper Flagg</v>
+        <v>LeBron James</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -29303,14 +29341,29 @@
         <v>14</v>
       </c>
       <c r="B194">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="C194">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D194">
+        <v>9500000</v>
+      </c>
+      <c r="F194">
+        <v>10500000</v>
+      </c>
+      <c r="G194" t="s">
+        <v>620</v>
+      </c>
+      <c r="H194">
+        <v>11500000</v>
+      </c>
+      <c r="I194" t="s">
+        <v>620</v>
       </c>
       <c r="L194" t="str">
         <f>VLOOKUP(B194,players!A:B,2)</f>
-        <v>Karl-Anthony Towns</v>
+        <v>Cooper Flagg</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -29318,14 +29371,14 @@
         <v>14</v>
       </c>
       <c r="B195">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="C195">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L195" t="str">
         <f>VLOOKUP(B195,players!A:B,2)</f>
-        <v>Quentin Grimes</v>
+        <v>Karl-Anthony Towns</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -29333,23 +29386,14 @@
         <v>14</v>
       </c>
       <c r="B196">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="C196">
-        <v>12</v>
-      </c>
-      <c r="D196">
-        <v>20000000</v>
-      </c>
-      <c r="F196">
-        <v>20000000</v>
-      </c>
-      <c r="H196">
-        <v>20000000</v>
+        <v>11</v>
       </c>
       <c r="L196" t="str">
         <f>VLOOKUP(B196,players!A:B,2)</f>
-        <v>LaMelo Ball</v>
+        <v>Quentin Grimes</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -29357,85 +29401,109 @@
         <v>14</v>
       </c>
       <c r="B197">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="C197">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D197">
-        <v>3200000</v>
+        <v>20000000</v>
       </c>
       <c r="F197">
-        <v>3500000</v>
+        <v>20000000</v>
+      </c>
+      <c r="H197">
+        <v>20000000</v>
       </c>
       <c r="L197" t="str">
         <f>VLOOKUP(B197,players!A:B,2)</f>
-        <v>Cason Wallace</v>
+        <v>LaMelo Ball</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198">
+        <v>14</v>
+      </c>
+      <c r="B198">
+        <v>273</v>
+      </c>
+      <c r="C198">
         <v>13</v>
       </c>
-      <c r="B198">
-        <v>426</v>
-      </c>
-      <c r="C198">
-        <v>14</v>
-      </c>
       <c r="D198">
-        <v>3400000</v>
+        <v>3200000</v>
       </c>
       <c r="F198">
-        <v>3600000</v>
-      </c>
-      <c r="H198">
-        <v>3800000</v>
-      </c>
-      <c r="I198" t="s">
-        <v>620</v>
-      </c>
-      <c r="J198">
-        <v>4100000</v>
-      </c>
-      <c r="K198" t="s">
-        <v>620</v>
+        <v>3500000</v>
       </c>
       <c r="L198" t="str">
         <f>VLOOKUP(B198,players!A:B,2)</f>
-        <v>Morez Johnson Jr.</v>
+        <v>Cason Wallace</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B199">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C199">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D199">
-        <v>1000000</v>
+        <v>3400000</v>
       </c>
       <c r="F199">
-        <v>1000000</v>
+        <v>3600000</v>
       </c>
       <c r="H199">
-        <v>1000000</v>
+        <v>3800000</v>
       </c>
       <c r="I199" t="s">
         <v>620</v>
       </c>
       <c r="J199">
-        <v>1000000</v>
+        <v>4100000</v>
       </c>
       <c r="K199" t="s">
         <v>620</v>
       </c>
       <c r="L199" t="str">
         <f>VLOOKUP(B199,players!A:B,2)</f>
+        <v>Morez Johnson Jr.</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>7</v>
+      </c>
+      <c r="B200">
+        <v>434</v>
+      </c>
+      <c r="C200">
+        <v>15</v>
+      </c>
+      <c r="D200">
+        <v>1000000</v>
+      </c>
+      <c r="F200">
+        <v>1000000</v>
+      </c>
+      <c r="H200">
+        <v>1000000</v>
+      </c>
+      <c r="I200" t="s">
+        <v>620</v>
+      </c>
+      <c r="J200">
+        <v>1000000</v>
+      </c>
+      <c r="K200" t="s">
+        <v>620</v>
+      </c>
+      <c r="L200" t="str">
+        <f>VLOOKUP(B200,players!A:B,2)</f>
         <v>Allen Graves</v>
       </c>
     </row>
